--- a/de.bund.bfr.knime.openkrise.db/src/de/bund/bfr/knime/openkrise/db/imports/custom/bfrnewformat/FCL_Uptrace_Prod_tob_es.xlsx
+++ b/de.bund.bfr.knime.openkrise.db/src/de/bund/bfr/knime/openkrise/db/imports/custom/bfrnewformat/FCL_Uptrace_Prod_tob_es.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC05EBE4-250E-4D60-8772-AD3FB7A4C112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28785" yWindow="480" windowWidth="28575" windowHeight="11670"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prod - Trazabilidadhaciadelante" sheetId="5" r:id="rId1"/>
@@ -12,7 +13,18 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Prod - Trazabilidadhaciadelante'!$A$1:$N$41</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -96,13 +108,7 @@
     <t>Entrada de mercancías</t>
   </si>
   <si>
-    <t>Para cualquier pregunta contacte con FoodRiskLabs-Team, +49 (30) 18412-4444, foodrisklabs@bfr.bund.de</t>
-  </si>
-  <si>
     <t>Año</t>
-  </si>
-  <si>
-    <t>En caso de poseer los datos requeridos en otro formato digital tales como en archivos Excel o XML, no será necesario rellenar este formulario. Por favor, contacte con nosotros (BfR FoodRiskLabs-Team, +49 (30) 18412-4444).</t>
   </si>
   <si>
     <t>Número de línea o número de lote de la mercancía de entrada</t>
@@ -110,11 +116,17 @@
   <si>
     <t>En la columna A introduzca a partir de la línea 18 el número de linea de la mercancía de entrada a la que esta asociada la mercancía de salida y rellene los campos desde la columna B en adelante con la información de entrada.</t>
   </si>
+  <si>
+    <t>Para cualquier pregunta contacte con FoodRiskLabs-Team, foodrisklabs@bfr.bund.de</t>
+  </si>
+  <si>
+    <t>En caso de poseer los datos requeridos en otro formato digital tales como en archivos Excel o XML, no será necesario rellenar este formulario. Por favor, contacte con nosotros.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1581,120 +1593,120 @@
     </xf>
   </cellXfs>
   <cellStyles count="114">
-    <cellStyle name="20% - Accent1 2" xfId="4"/>
-    <cellStyle name="20% - Accent2 2" xfId="5"/>
-    <cellStyle name="20% - Accent3 2" xfId="6"/>
-    <cellStyle name="20% - Accent4 2" xfId="7"/>
-    <cellStyle name="20% - Accent5 2" xfId="8"/>
-    <cellStyle name="20% - Accent6 2" xfId="9"/>
-    <cellStyle name="40% - Accent1 2" xfId="10"/>
-    <cellStyle name="40% - Accent2 2" xfId="11"/>
-    <cellStyle name="40% - Accent3 2" xfId="12"/>
-    <cellStyle name="40% - Accent4 2" xfId="13"/>
-    <cellStyle name="40% - Accent5 2" xfId="14"/>
-    <cellStyle name="40% - Accent6 2" xfId="15"/>
-    <cellStyle name="60% - Accent1 2" xfId="16"/>
-    <cellStyle name="60% - Accent2 2" xfId="17"/>
-    <cellStyle name="60% - Accent3 2" xfId="18"/>
-    <cellStyle name="60% - Accent4 2" xfId="19"/>
-    <cellStyle name="60% - Accent5 2" xfId="20"/>
-    <cellStyle name="60% - Accent6 2" xfId="21"/>
-    <cellStyle name="Accent1 2" xfId="22"/>
-    <cellStyle name="Accent2 2" xfId="23"/>
-    <cellStyle name="Accent3 2" xfId="24"/>
-    <cellStyle name="Accent4 2" xfId="25"/>
-    <cellStyle name="Accent5 2" xfId="26"/>
-    <cellStyle name="Accent6 2" xfId="27"/>
-    <cellStyle name="Bad 2" xfId="28"/>
-    <cellStyle name="Calculation 2" xfId="29"/>
-    <cellStyle name="Check Cell 2" xfId="30"/>
-    <cellStyle name="Explanatory Text 2" xfId="31"/>
-    <cellStyle name="Good 2" xfId="32"/>
-    <cellStyle name="Heading 1 2" xfId="33"/>
-    <cellStyle name="Heading 2 2" xfId="34"/>
-    <cellStyle name="Heading 3 2" xfId="35"/>
-    <cellStyle name="Heading 4 2" xfId="36"/>
-    <cellStyle name="Input 2" xfId="37"/>
-    <cellStyle name="Linked Cell 2" xfId="38"/>
-    <cellStyle name="Neutral 2" xfId="39"/>
-    <cellStyle name="Normal 10" xfId="40"/>
-    <cellStyle name="Normal 10 2" xfId="41"/>
-    <cellStyle name="Normal 10 2 2" xfId="42"/>
-    <cellStyle name="Normal 10 2 3" xfId="43"/>
-    <cellStyle name="Normal 10 3" xfId="44"/>
-    <cellStyle name="Normal 10 4" xfId="45"/>
-    <cellStyle name="Normal 11" xfId="46"/>
-    <cellStyle name="Normal 11 2" xfId="47"/>
-    <cellStyle name="Normal 11 2 2" xfId="48"/>
-    <cellStyle name="Normal 11 2 3" xfId="49"/>
-    <cellStyle name="Normal 11 3" xfId="50"/>
-    <cellStyle name="Normal 11 4" xfId="51"/>
-    <cellStyle name="Normal 12" xfId="52"/>
-    <cellStyle name="Normal 12 2" xfId="53"/>
-    <cellStyle name="Normal 12 3" xfId="54"/>
-    <cellStyle name="Normal 12 4" xfId="55"/>
-    <cellStyle name="Normal 13" xfId="56"/>
-    <cellStyle name="Normal 13 2" xfId="57"/>
-    <cellStyle name="Normal 13 3" xfId="58"/>
-    <cellStyle name="Normal 13 4" xfId="59"/>
-    <cellStyle name="Normal 14" xfId="60"/>
-    <cellStyle name="Normal 14 2" xfId="61"/>
-    <cellStyle name="Normal 15" xfId="62"/>
-    <cellStyle name="Normal 15 2" xfId="63"/>
-    <cellStyle name="Normal 16" xfId="64"/>
-    <cellStyle name="Normal 17" xfId="65"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="67"/>
-    <cellStyle name="Normal 2 2 2" xfId="68"/>
-    <cellStyle name="Normal 2 2 3" xfId="69"/>
-    <cellStyle name="Normal 2 3" xfId="70"/>
-    <cellStyle name="Normal 2 3 2" xfId="71"/>
-    <cellStyle name="Normal 2 3 3" xfId="72"/>
-    <cellStyle name="Normal 2 4" xfId="73"/>
-    <cellStyle name="Normal 2 5" xfId="74"/>
-    <cellStyle name="Normal 2 6" xfId="66"/>
-    <cellStyle name="Normal 3" xfId="1"/>
-    <cellStyle name="Normal 3 2" xfId="76"/>
-    <cellStyle name="Normal 3 3" xfId="77"/>
-    <cellStyle name="Normal 3 4" xfId="75"/>
-    <cellStyle name="Normal 4" xfId="78"/>
-    <cellStyle name="Normal 4 2" xfId="79"/>
-    <cellStyle name="Normal 4 3" xfId="80"/>
-    <cellStyle name="Normal 5" xfId="81"/>
-    <cellStyle name="Normal 6" xfId="82"/>
-    <cellStyle name="Normal 6 2" xfId="83"/>
-    <cellStyle name="Normal 6 3" xfId="84"/>
-    <cellStyle name="Normal 7" xfId="85"/>
-    <cellStyle name="Normal 7 2" xfId="86"/>
-    <cellStyle name="Normal 7 2 2" xfId="87"/>
-    <cellStyle name="Normal 7 2 3" xfId="88"/>
-    <cellStyle name="Normal 7 3" xfId="89"/>
-    <cellStyle name="Normal 7 3 2" xfId="90"/>
-    <cellStyle name="Normal 7 3 3" xfId="91"/>
-    <cellStyle name="Normal 7 4" xfId="92"/>
-    <cellStyle name="Normal 7 5" xfId="93"/>
-    <cellStyle name="Normal 8" xfId="94"/>
-    <cellStyle name="Normal 8 2" xfId="95"/>
-    <cellStyle name="Normal 8 2 2" xfId="96"/>
-    <cellStyle name="Normal 8 2 3" xfId="97"/>
-    <cellStyle name="Normal 8 3" xfId="98"/>
-    <cellStyle name="Normal 8 4" xfId="99"/>
-    <cellStyle name="Normal 9" xfId="100"/>
-    <cellStyle name="Normal 9 2" xfId="101"/>
-    <cellStyle name="Normal 9 2 2" xfId="102"/>
-    <cellStyle name="Normal 9 2 3" xfId="103"/>
-    <cellStyle name="Normal 9 3" xfId="104"/>
-    <cellStyle name="Normal 9 4" xfId="105"/>
-    <cellStyle name="Note 2" xfId="106"/>
-    <cellStyle name="Notiz 2" xfId="113"/>
-    <cellStyle name="Output 2" xfId="107"/>
-    <cellStyle name="Standaard_Business_List" xfId="108"/>
+    <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Accent2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Accent4 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent5 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - Accent1 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - Accent2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - Accent3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - Accent4 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - Accent5 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - Accent6 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Accent1 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Accent2 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Accent3 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Accent4 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Accent5 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Accent6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Bad 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Calculation 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Check Cell 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Explanatory Text 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Good 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Heading 1 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Heading 2 2" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Heading 3 2" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Heading 4 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Input 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Linked Cell 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Neutral 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 10" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normal 10 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 10 2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal 10 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Normal 10 3" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Normal 10 4" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Normal 11" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Normal 11 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Normal 11 2 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Normal 11 2 3" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Normal 11 3" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Normal 11 4" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Normal 12" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Normal 12 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 12 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 12 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 13" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 13 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 13 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 13 4" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Normal 14" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Normal 14 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Normal 15" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="Normal 15 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="Normal 16" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="Normal 17" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="Normal 2 2" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="Normal 2 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="Normal 2 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Normal 2 5" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Normal 2 6" xfId="66" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Normal 3 2" xfId="76" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Normal 3 3" xfId="77" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Normal 3 4" xfId="75" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Normal 4" xfId="78" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Normal 4 2" xfId="79" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Normal 4 3" xfId="80" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Normal 5" xfId="81" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Normal 6" xfId="82" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Normal 6 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Normal 6 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Normal 7" xfId="85" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Normal 7 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Normal 7 2 2" xfId="87" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Normal 7 2 3" xfId="88" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Normal 7 3" xfId="89" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Normal 7 3 2" xfId="90" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Normal 7 3 3" xfId="91" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Normal 7 4" xfId="92" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Normal 7 5" xfId="93" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Normal 8" xfId="94" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Normal 8 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Normal 8 2 2" xfId="96" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Normal 8 2 3" xfId="97" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Normal 8 3" xfId="98" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Normal 8 4" xfId="99" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Normal 9" xfId="100" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Normal 9 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Normal 9 2 2" xfId="102" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Normal 9 2 3" xfId="103" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Normal 9 3" xfId="104" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="Normal 9 4" xfId="105" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Note 2" xfId="106" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Notiz 2" xfId="113" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Output 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Standaard_Business_List" xfId="108" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Standard 2" xfId="3"/>
-    <cellStyle name="Standard 3" xfId="112"/>
-    <cellStyle name="Title 2" xfId="109"/>
-    <cellStyle name="Total 2" xfId="110"/>
-    <cellStyle name="Warning Text 2" xfId="111"/>
+    <cellStyle name="Standard 2" xfId="3" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Standard 3" xfId="112" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Title 2" xfId="109" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Total 2" xfId="110" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Warning Text 2" xfId="111" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1702,14 +1714,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1747,9 +1762,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1782,9 +1797,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1817,9 +1849,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1992,28 +2041,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="12.75" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.86328125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.3984375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="12" style="2" customWidth="1"/>
-    <col min="6" max="6" width="4.3984375" style="42" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.73046875" style="42" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.265625" style="42" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1328125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.86328125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="32.73046875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.86328125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="42.86328125" style="2" customWidth="1"/>
-    <col min="15" max="19" width="11.3984375" style="1"/>
-    <col min="20" max="16384" width="11.3984375" style="2"/>
+    <col min="6" max="6" width="4.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" style="42" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="32.7109375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="42.85546875" style="2" customWidth="1"/>
+    <col min="15" max="19" width="11.42578125" style="1"/>
+    <col min="20" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="10" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2041,7 +2090,7 @@
     </row>
     <row r="2" spans="1:19" s="12" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="55" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -2062,7 +2111,7 @@
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
     </row>
-    <row r="3" spans="1:19" s="14" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19" s="14" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="74" t="s">
         <v>24</v>
       </c>
@@ -2085,7 +2134,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="86" t="s">
         <v>1</v>
       </c>
@@ -2114,7 +2163,7 @@
       </c>
       <c r="O4" s="13"/>
     </row>
-    <row r="5" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="86"/>
       <c r="B5" s="67" t="s">
         <v>8</v>
@@ -2151,7 +2200,7 @@
       <c r="N5" s="84"/>
       <c r="O5" s="13"/>
     </row>
-    <row r="6" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="88"/>
       <c r="B6" s="67"/>
       <c r="C6" s="67"/>
@@ -2164,7 +2213,7 @@
         <v>17</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" s="67"/>
       <c r="J6" s="92"/>
@@ -2197,7 +2246,7 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="78" t="s">
         <v>22</v>
       </c>
@@ -2215,7 +2264,7 @@
       <c r="M8" s="79"/>
       <c r="N8" s="80"/>
     </row>
-    <row r="9" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="81" t="s">
         <v>20</v>
       </c>
@@ -2233,7 +2282,7 @@
       <c r="M9" s="82"/>
       <c r="N9" s="83"/>
     </row>
-    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="81" t="s">
         <v>18</v>
       </c>
@@ -2251,9 +2300,9 @@
       <c r="M10" s="82"/>
       <c r="N10" s="83"/>
     </row>
-    <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="82"/>
       <c r="C11" s="82"/>
@@ -2269,7 +2318,7 @@
       <c r="M11" s="82"/>
       <c r="N11" s="83"/>
     </row>
-    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="81" t="s">
         <v>19</v>
       </c>
@@ -2287,9 +2336,9 @@
       <c r="M12" s="82"/>
       <c r="N12" s="83"/>
     </row>
-    <row r="13" spans="1:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="81" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="82"/>
       <c r="C13" s="82"/>
@@ -2306,7 +2355,7 @@
       <c r="N13" s="83"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="74" t="s">
         <v>23</v>
       </c>
@@ -2325,9 +2374,9 @@
       <c r="N14" s="77"/>
       <c r="O14" s="13"/>
     </row>
-    <row r="15" spans="1:19" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:19" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="85" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" s="59" t="s">
         <v>3</v>
@@ -2358,7 +2407,7 @@
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
     </row>
-    <row r="16" spans="1:19" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:19" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="86"/>
       <c r="B16" s="65" t="s">
         <v>8</v>
@@ -2399,7 +2448,7 @@
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
     </row>
-    <row r="17" spans="1:19" s="5" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:19" s="5" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="87"/>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
@@ -2412,7 +2461,7 @@
         <v>17</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I17" s="72"/>
       <c r="J17" s="66"/>
@@ -2800,7 +2849,7 @@
       <c r="N39" s="34"/>
       <c r="O39" s="13"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
@@ -2817,7 +2866,7 @@
       <c r="N40" s="34"/>
       <c r="O40" s="13"/>
     </row>
-    <row r="41" spans="1:15" ht="13.15" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="36"/>
       <c r="B41" s="37"/>
       <c r="C41" s="37"/>
@@ -2883,15 +2932,15 @@
     <mergeCell ref="A2:N2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7 F14 F3 F18:F1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7 F14 F3 F18:F1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>31</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7 G14 G3 G18:G1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7 G14 G3 G18:G1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>1</formula1>
       <formula2>12</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14 H7 H3 H18:H1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H14 H7 H3 H18:H1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>1900</formula1>
       <formula2>2100</formula2>
     </dataValidation>
